--- a/hotel_booking_feedback.xlsx
+++ b/hotel_booking_feedback.xlsx
@@ -1621,8 +1621,1508 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="0" t="inlineStr">
+        <is>
+          <t>FB-051</t>
+        </is>
+      </c>
+      <c r="B52" s="0" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C52" s="0" t="inlineStr">
+        <is>
+          <t>Application UI</t>
+        </is>
+      </c>
+      <c r="D52" s="2">
+        <v>2</v>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>The search results occasionally disappear after I change the dates.</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="0" t="inlineStr">
+        <is>
+          <t>FB-052</t>
+        </is>
+      </c>
+      <c r="B53" s="0" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="C53" s="0" t="inlineStr">
+        <is>
+          <t>Application UI</t>
+        </is>
+      </c>
+      <c r="D53" s="2">
+        <v>2</v>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>The mobile menu closes before I can select an option.</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="0" t="inlineStr">
+        <is>
+          <t>FB-053</t>
+        </is>
+      </c>
+      <c r="B54" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C54" s="0" t="inlineStr">
+        <is>
+          <t>Application UI</t>
+        </is>
+      </c>
+      <c r="D54" s="2">
+        <v>1</v>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>The booking page freezes when I try to compare rooms.</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="0" t="inlineStr">
+        <is>
+          <t>FB-054</t>
+        </is>
+      </c>
+      <c r="B55" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C55" s="0" t="inlineStr">
+        <is>
+          <t>Application UI</t>
+        </is>
+      </c>
+      <c r="D55" s="2">
+        <v>2</v>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>The availability calendar shows rooms that cannot be booked.</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="0" t="inlineStr">
+        <is>
+          <t>FB-055</t>
+        </is>
+      </c>
+      <c r="B56" s="0" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="C56" s="0" t="inlineStr">
+        <is>
+          <t>Application UI</t>
+        </is>
+      </c>
+      <c r="D56" s="2">
+        <v>2</v>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>The filter controls are difficult to use on a small screen.</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="0" t="inlineStr">
+        <is>
+          <t>FB-056</t>
+        </is>
+      </c>
+      <c r="B57" s="0" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="C57" s="0" t="inlineStr">
+        <is>
+          <t>Application UI</t>
+        </is>
+      </c>
+      <c r="D57" s="2">
+        <v>1</v>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>My selected hotel was lost when I returned to the search results.</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="0" t="inlineStr">
+        <is>
+          <t>FB-057</t>
+        </is>
+      </c>
+      <c r="B58" s="0" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C58" s="0" t="inlineStr">
+        <is>
+          <t>Application UI</t>
+        </is>
+      </c>
+      <c r="D58" s="2">
+        <v>2</v>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>The page displayed an error while loading room details.</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="0" t="inlineStr">
+        <is>
+          <t>FB-058</t>
+        </is>
+      </c>
+      <c r="B59" s="0" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C59" s="0" t="inlineStr">
+        <is>
+          <t>Application UI</t>
+        </is>
+      </c>
+      <c r="D59" s="2">
+        <v>2</v>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>The sort order resets whenever I open a room listing.</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="0" t="inlineStr">
+        <is>
+          <t>FB-059</t>
+        </is>
+      </c>
+      <c r="B60" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C60" s="0" t="inlineStr">
+        <is>
+          <t>Application UI</t>
+        </is>
+      </c>
+      <c r="D60" s="2">
+        <v>1</v>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>The checkout button was unresponsive for several minutes.</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="0" t="inlineStr">
+        <is>
+          <t>FB-060</t>
+        </is>
+      </c>
+      <c r="B61" s="0" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C61" s="0" t="inlineStr">
+        <is>
+          <t>Application UI</t>
+        </is>
+      </c>
+      <c r="D61" s="2">
+        <v>2</v>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>Important booking information is hidden below an unclear link.</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="0" t="inlineStr">
+        <is>
+          <t>FB-061</t>
+        </is>
+      </c>
+      <c r="B62" s="0" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="C62" s="0" t="inlineStr">
+        <is>
+          <t>User-friendly</t>
+        </is>
+      </c>
+      <c r="D62" s="2">
+        <v>2</v>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>The instructions were confusing when I tried to change my dates.</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="0" t="inlineStr">
+        <is>
+          <t>FB-062</t>
+        </is>
+      </c>
+      <c r="B63" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C63" s="0" t="inlineStr">
+        <is>
+          <t>User-friendly</t>
+        </is>
+      </c>
+      <c r="D63" s="2">
+        <v>2</v>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>I could not understand which fields were required on the booking form.</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="0" t="inlineStr">
+        <is>
+          <t>FB-063</t>
+        </is>
+      </c>
+      <c r="B64" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C64" s="0" t="inlineStr">
+        <is>
+          <t>User-friendly</t>
+        </is>
+      </c>
+      <c r="D64" s="2">
+        <v>1</v>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>The sign-up process rejected my details without explaining why.</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="0" t="inlineStr">
+        <is>
+          <t>FB-064</t>
+        </is>
+      </c>
+      <c r="B65" s="0" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="C65" s="0" t="inlineStr">
+        <is>
+          <t>User-friendly</t>
+        </is>
+      </c>
+      <c r="D65" s="2">
+        <v>2</v>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>Cancellation options were difficult to find before payment.</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="0" t="inlineStr">
+        <is>
+          <t>FB-065</t>
+        </is>
+      </c>
+      <c r="B66" s="0" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="C66" s="0" t="inlineStr">
+        <is>
+          <t>User-friendly</t>
+        </is>
+      </c>
+      <c r="D66" s="2">
+        <v>2</v>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>The wording on the checkout page caused me to enter information twice.</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="0" t="inlineStr">
+        <is>
+          <t>FB-066</t>
+        </is>
+      </c>
+      <c r="B67" s="0" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C67" s="0" t="inlineStr">
+        <is>
+          <t>User-friendly</t>
+        </is>
+      </c>
+      <c r="D67" s="2">
+        <v>1</v>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>The application gave no useful guidance after my booking failed.</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="0" t="inlineStr">
+        <is>
+          <t>FB-067</t>
+        </is>
+      </c>
+      <c r="B68" s="0" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C68" s="0" t="inlineStr">
+        <is>
+          <t>User-friendly</t>
+        </is>
+      </c>
+      <c r="D68" s="2">
+        <v>2</v>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>It was unclear whether my reservation had been confirmed.</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="0" t="inlineStr">
+        <is>
+          <t>FB-068</t>
+        </is>
+      </c>
+      <c r="B69" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C69" s="0" t="inlineStr">
+        <is>
+          <t>User-friendly</t>
+        </is>
+      </c>
+      <c r="D69" s="2">
+        <v>2</v>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>The help text did not explain the required document format.</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="0" t="inlineStr">
+        <is>
+          <t>FB-069</t>
+        </is>
+      </c>
+      <c r="B70" s="0" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C70" s="0" t="inlineStr">
+        <is>
+          <t>User-friendly</t>
+        </is>
+      </c>
+      <c r="D70" s="2">
+        <v>1</v>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>I had to restart the reservation several times to complete it.</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="0" t="inlineStr">
+        <is>
+          <t>FB-070</t>
+        </is>
+      </c>
+      <c r="B71" s="0" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="C71" s="0" t="inlineStr">
+        <is>
+          <t>User-friendly</t>
+        </is>
+      </c>
+      <c r="D71" s="2">
+        <v>2</v>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>The checkout terminology was confusing and inconsistent.</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="0" t="inlineStr">
+        <is>
+          <t>FB-071</t>
+        </is>
+      </c>
+      <c r="B72" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C72" s="0" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="D72" s="2">
+        <v>2</v>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>The payment page rejected my card without giving a clear reason.</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="0" t="inlineStr">
+        <is>
+          <t>FB-072</t>
+        </is>
+      </c>
+      <c r="B73" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C73" s="0" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="D73" s="2">
+        <v>1</v>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>A service charge appeared only after I entered my payment details.</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="0" t="inlineStr">
+        <is>
+          <t>FB-073</t>
+        </is>
+      </c>
+      <c r="B74" s="0" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="C74" s="0" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="D74" s="2">
+        <v>2</v>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>The refund amount did not match the amount shown in the cancellation summary.</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="0" t="inlineStr">
+        <is>
+          <t>FB-074</t>
+        </is>
+      </c>
+      <c r="B75" s="0" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="C75" s="0" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="D75" s="2">
+        <v>2</v>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>The invoice contained an incorrect company name.</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="0" t="inlineStr">
+        <is>
+          <t>FB-075</t>
+        </is>
+      </c>
+      <c r="B76" s="0" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C76" s="0" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="D76" s="2">
+        <v>1</v>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>My payment was taken but the reservation was not created.</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="0" t="inlineStr">
+        <is>
+          <t>FB-076</t>
+        </is>
+      </c>
+      <c r="B77" s="0" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C77" s="0" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="D77" s="2">
+        <v>2</v>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>The exchange rate used at checkout was not clearly disclosed.</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="0" t="inlineStr">
+        <is>
+          <t>FB-077</t>
+        </is>
+      </c>
+      <c r="B78" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C78" s="0" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="D78" s="2">
+        <v>2</v>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>The deposit hold remained on my account longer than promised.</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="0" t="inlineStr">
+        <is>
+          <t>FB-078</t>
+        </is>
+      </c>
+      <c r="B79" s="0" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C79" s="0" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="D79" s="2">
+        <v>1</v>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>I received duplicate receipts for one booking.</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="0" t="inlineStr">
+        <is>
+          <t>FB-079</t>
+        </is>
+      </c>
+      <c r="B80" s="0" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="C80" s="0" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="D80" s="2">
+        <v>2</v>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>The total changed again when I selected a different payment method.</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="0" t="inlineStr">
+        <is>
+          <t>FB-080</t>
+        </is>
+      </c>
+      <c r="B81" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C81" s="0" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="D81" s="2">
+        <v>1</v>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>Support could not explain an unexpected charge on my statement.</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="0" t="inlineStr">
+        <is>
+          <t>FB-081</t>
+        </is>
+      </c>
+      <c r="B82" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C82" s="0" t="inlineStr">
+        <is>
+          <t>Rooms</t>
+        </is>
+      </c>
+      <c r="D82" s="2">
+        <v>2</v>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>The room was not ready when I arrived for check-in.</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="0" t="inlineStr">
+        <is>
+          <t>FB-082</t>
+        </is>
+      </c>
+      <c r="B83" s="0" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="C83" s="0" t="inlineStr">
+        <is>
+          <t>Rooms</t>
+        </is>
+      </c>
+      <c r="D83" s="2">
+        <v>1</v>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>The room had a strong odor that staff did not resolve.</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="0" t="inlineStr">
+        <is>
+          <t>FB-083</t>
+        </is>
+      </c>
+      <c r="B84" s="0" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="C84" s="0" t="inlineStr">
+        <is>
+          <t>Rooms</t>
+        </is>
+      </c>
+      <c r="D84" s="2">
+        <v>2</v>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>Several advertised amenities were missing from the room.</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="0" t="inlineStr">
+        <is>
+          <t>FB-084</t>
+        </is>
+      </c>
+      <c r="B85" s="0" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C85" s="0" t="inlineStr">
+        <is>
+          <t>Rooms</t>
+        </is>
+      </c>
+      <c r="D85" s="2">
+        <v>2</v>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>The heating system stopped working during the night.</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="0" t="inlineStr">
+        <is>
+          <t>FB-085</t>
+        </is>
+      </c>
+      <c r="B86" s="0" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C86" s="0" t="inlineStr">
+        <is>
+          <t>Rooms</t>
+        </is>
+      </c>
+      <c r="D86" s="2">
+        <v>1</v>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>The room was not cleaned properly before my arrival.</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="0" t="inlineStr">
+        <is>
+          <t>FB-086</t>
+        </is>
+      </c>
+      <c r="B87" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C87" s="0" t="inlineStr">
+        <is>
+          <t>Rooms</t>
+        </is>
+      </c>
+      <c r="D87" s="2">
+        <v>2</v>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>Construction noise made it difficult to sleep.</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="0" t="inlineStr">
+        <is>
+          <t>FB-087</t>
+        </is>
+      </c>
+      <c r="B88" s="0" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C88" s="0" t="inlineStr">
+        <is>
+          <t>Rooms</t>
+        </is>
+      </c>
+      <c r="D88" s="2">
+        <v>2</v>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>The room description overstated the size and available space.</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="0" t="inlineStr">
+        <is>
+          <t>FB-088</t>
+        </is>
+      </c>
+      <c r="B89" s="0" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="C89" s="0" t="inlineStr">
+        <is>
+          <t>Rooms</t>
+        </is>
+      </c>
+      <c r="D89" s="2">
+        <v>1</v>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>The shower had low water pressure and inconsistent temperature.</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="0" t="inlineStr">
+        <is>
+          <t>FB-089</t>
+        </is>
+      </c>
+      <c r="B90" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C90" s="0" t="inlineStr">
+        <is>
+          <t>Rooms</t>
+        </is>
+      </c>
+      <c r="D90" s="2">
+        <v>2</v>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>The requested room arrangement was not available at check-in.</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="0" t="inlineStr">
+        <is>
+          <t>FB-090</t>
+        </is>
+      </c>
+      <c r="B91" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C91" s="0" t="inlineStr">
+        <is>
+          <t>Rooms</t>
+        </is>
+      </c>
+      <c r="D91" s="2">
+        <v>1</v>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>The air conditioning leaked water onto the floor.</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="0" t="inlineStr">
+        <is>
+          <t>FB-091</t>
+        </is>
+      </c>
+      <c r="B92" s="0" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="C92" s="0" t="inlineStr">
+        <is>
+          <t>Customer Assistance</t>
+        </is>
+      </c>
+      <c r="D92" s="2">
+        <v>2</v>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>My support request received no response for two days.</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="0" t="inlineStr">
+        <is>
+          <t>FB-092</t>
+        </is>
+      </c>
+      <c r="B93" s="0" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="C93" s="0" t="inlineStr">
+        <is>
+          <t>Customer Assistance</t>
+        </is>
+      </c>
+      <c r="D93" s="2">
+        <v>1</v>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>The first agent closed my case without resolving the issue.</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="0" t="inlineStr">
+        <is>
+          <t>FB-093</t>
+        </is>
+      </c>
+      <c r="B94" s="0" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C94" s="0" t="inlineStr">
+        <is>
+          <t>Customer Assistance</t>
+        </is>
+      </c>
+      <c r="D94" s="2">
+        <v>2</v>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>I had to repeat the same problem to several agents.</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="0" t="inlineStr">
+        <is>
+          <t>FB-094</t>
+        </is>
+      </c>
+      <c r="B95" s="0" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C95" s="0" t="inlineStr">
+        <is>
+          <t>Customer Assistance</t>
+        </is>
+      </c>
+      <c r="D95" s="2">
+        <v>2</v>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>The help center provided outdated instructions.</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="0" t="inlineStr">
+        <is>
+          <t>FB-095</t>
+        </is>
+      </c>
+      <c r="B96" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C96" s="0" t="inlineStr">
+        <is>
+          <t>Customer Assistance</t>
+        </is>
+      </c>
+      <c r="D96" s="2">
+        <v>1</v>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>The support chat disconnected before my issue was resolved.</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="0" t="inlineStr">
+        <is>
+          <t>FB-096</t>
+        </is>
+      </c>
+      <c r="B97" s="0" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C97" s="0" t="inlineStr">
+        <is>
+          <t>Customer Assistance</t>
+        </is>
+      </c>
+      <c r="D97" s="2">
+        <v>2</v>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>No one followed up after promising to investigate the problem.</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="0" t="inlineStr">
+        <is>
+          <t>FB-097</t>
+        </is>
+      </c>
+      <c r="B98" s="0" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="C98" s="0" t="inlineStr">
+        <is>
+          <t>Customer Assistance</t>
+        </is>
+      </c>
+      <c r="D98" s="2">
+        <v>1</v>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>The agent gave incorrect information about the cancellation policy.</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="0" t="inlineStr">
+        <is>
+          <t>FB-098</t>
+        </is>
+      </c>
+      <c r="B99" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C99" s="0" t="inlineStr">
+        <is>
+          <t>Customer Assistance</t>
+        </is>
+      </c>
+      <c r="D99" s="2">
+        <v>2</v>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>It was impossible to reach a human agent through the help center.</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="0" t="inlineStr">
+        <is>
+          <t>FB-099</t>
+        </is>
+      </c>
+      <c r="B100" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C100" s="0" t="inlineStr">
+        <is>
+          <t>Customer Assistance</t>
+        </is>
+      </c>
+      <c r="D100" s="2">
+        <v>2</v>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>My complaint was transferred without any explanation.</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="0" t="inlineStr">
+        <is>
+          <t>FB-100</t>
+        </is>
+      </c>
+      <c r="B101" s="0" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="C101" s="0" t="inlineStr">
+        <is>
+          <t>Customer Assistance</t>
+        </is>
+      </c>
+      <c r="D101" s="2">
+        <v>1</v>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>The support team refused to investigate an incorrect charge.</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F51"/>
+  <autoFilter ref="A1:F101"/>
 </worksheet>
 </file>
 
@@ -1665,10 +3165,10 @@
         </is>
       </c>
       <c r="B4" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C4" s="2">
-        <v>4.0</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="5">
@@ -1678,10 +3178,10 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C5" s="2">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="6">
@@ -1691,10 +3191,10 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C6" s="2">
-        <v>4.0</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="7">
@@ -1704,10 +3204,10 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C7" s="2">
-        <v>4.0</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="8">
@@ -1717,10 +3217,10 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C8" s="2">
-        <v>4.0</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="10">
@@ -1730,10 +3230,10 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C10" s="2">
-        <v>4.02</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="12">
